--- a/projects/register-room-update/All_Buildings_Rooms_Inclusion_Status_V1.3.xlsx
+++ b/projects/register-room-update/All_Buildings_Rooms_Inclusion_Status_V1.3.xlsx
@@ -48280,7 +48280,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>RDC_NB_AHU8511</t>
+          <t>RDC_NB_2F_AHU8511</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -48317,7 +48317,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>RDC_NB_AHU8512</t>
+          <t>RDC_NB_2F_AHU8512</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -48354,7 +48354,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>RDC_NB_2F_2F_AHU8513</t>
+          <t>RDC_NB_2F_AHU8513</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">

--- a/projects/register-room-update/All_Buildings_Rooms_Inclusion_Status_V1.3.xlsx
+++ b/projects/register-room-update/All_Buildings_Rooms_Inclusion_Status_V1.3.xlsx
@@ -4297,7 +4297,11 @@
           <t>FCU</t>
         </is>
       </c>
-      <c r="C125" s="5" t="n"/>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
           <t>B1.512 IDF ROOM</t>
@@ -40870,7 +40874,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C454" s="5" t="n"/>
+      <c r="C454" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D454" s="5" t="inlineStr">
         <is>
           <t>B.035 CORRIDOR 4</t>
@@ -40896,7 +40904,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C455" s="5" t="n"/>
+      <c r="C455" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D455" s="5" t="inlineStr">
         <is>
           <t>B.035 CORRIDOR 4</t>
@@ -40922,7 +40934,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C456" s="5" t="n"/>
+      <c r="C456" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D456" s="5" t="inlineStr">
         <is>
           <t>B.095 EMERGENCY LIGHTING BATTERY ROOM</t>
@@ -40948,7 +40964,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C457" s="5" t="n"/>
+      <c r="C457" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
           <t>B.082 TRANSFORMER ROOM</t>
@@ -40974,7 +40994,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C458" s="5" t="n"/>
+      <c r="C458" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D458" s="5" t="inlineStr">
         <is>
           <t>B.083 HV ROOM</t>
@@ -41000,7 +41024,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C459" s="5" t="n"/>
+      <c r="C459" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D459" s="5" t="inlineStr">
         <is>
           <t>B.083 HV ROOM</t>
@@ -41026,7 +41054,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C460" s="5" t="n"/>
+      <c r="C460" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D460" s="5" t="inlineStr">
         <is>
           <t>B.095 EMERGENCY LIGHTING BATTERY ROOM</t>
@@ -41052,7 +41084,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C461" s="5" t="n"/>
+      <c r="C461" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D461" s="5" t="inlineStr">
         <is>
           <t>B.095 EMERGENCY LIGHTING BATTERY ROOM</t>
@@ -41078,7 +41114,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C462" s="5" t="n"/>
+      <c r="C462" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D462" s="5" t="inlineStr">
         <is>
           <t>B.084 UPS BATTERY ROOM</t>
@@ -41104,7 +41144,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C463" s="5" t="n"/>
+      <c r="C463" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D463" s="5" t="inlineStr">
         <is>
           <t>B.103 PROCESSING ROOM</t>
@@ -41130,7 +41174,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C464" s="5" t="n"/>
+      <c r="C464" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D464" s="5" t="inlineStr">
         <is>
           <t>B.107 SECURITY EQUIPMENT ROOM</t>
@@ -41156,7 +41204,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C465" s="5" t="n"/>
+      <c r="C465" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D465" s="5" t="inlineStr">
         <is>
           <t>B.107 SECURITY EQUIPMENT ROOM</t>
@@ -41182,7 +41234,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C466" s="5" t="n"/>
+      <c r="C466" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D466" s="5" t="inlineStr">
         <is>
           <t>B.093 TRANSH CHAMBER</t>
@@ -41208,7 +41264,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C467" s="5" t="n"/>
+      <c r="C467" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D467" s="5" t="inlineStr">
         <is>
           <t>B.095 EMERGENCY LIGHTING BATTERY ROOM</t>
@@ -41234,7 +41294,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C468" s="5" t="n"/>
+      <c r="C468" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D468" s="5" t="inlineStr">
         <is>
           <t>B.093 TRANSH CHAMBER</t>
@@ -41260,7 +41324,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C469" s="5" t="n"/>
+      <c r="C469" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D469" s="5" t="inlineStr">
         <is>
           <t>B.095 EMERGENCY LIGHTING BATTERY ROOM</t>
@@ -41286,7 +41354,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C470" s="5" t="n"/>
+      <c r="C470" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D470" s="5" t="inlineStr">
         <is>
           <t>B.045A REFRIGERATE STORE</t>
@@ -41312,7 +41384,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C471" s="5" t="n"/>
+      <c r="C471" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D471" s="5" t="inlineStr">
         <is>
           <t>B.045A REFRIGERATE STORE</t>
@@ -41338,7 +41414,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C472" s="5" t="n"/>
+      <c r="C472" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D472" s="5" t="inlineStr">
         <is>
           <t>B.045A REFRIGERATE STORE</t>
@@ -41364,7 +41444,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C473" s="5" t="n"/>
+      <c r="C473" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D473" s="5" t="inlineStr">
         <is>
           <t>B.092 STORAGE</t>
@@ -41390,7 +41474,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C474" s="5" t="n"/>
+      <c r="C474" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D474" s="5" t="inlineStr">
         <is>
           <t>P.004 PLANT ZONE</t>
@@ -41416,7 +41504,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C475" s="5" t="n"/>
+      <c r="C475" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D475" s="5" t="inlineStr">
         <is>
           <t>B.106 REST ROOM SECURITY</t>
@@ -41442,7 +41534,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C476" s="5" t="n"/>
+      <c r="C476" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D476" s="5" t="inlineStr">
         <is>
           <t>B.107 SECURITY EQUIPMENT ROOM</t>
@@ -41468,7 +41564,11 @@
           <t>DX Unit</t>
         </is>
       </c>
-      <c r="C477" s="5" t="n"/>
+      <c r="C477" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D477" s="5" t="inlineStr">
         <is>
           <t>P.004 PLANT ZONE</t>
@@ -41494,7 +41594,11 @@
           <t>HEX</t>
         </is>
       </c>
-      <c r="C478" s="5" t="n"/>
+      <c r="C478" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D478" s="5" t="inlineStr">
         <is>
           <t>B.220 PLANT ROOM 04</t>
@@ -41520,7 +41624,11 @@
           <t>HEX</t>
         </is>
       </c>
-      <c r="C479" s="5" t="n"/>
+      <c r="C479" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D479" s="5" t="inlineStr">
         <is>
           <t>B.220 PLANT ROOM 04</t>
@@ -41546,7 +41654,11 @@
           <t>HEX</t>
         </is>
       </c>
-      <c r="C480" s="5" t="n"/>
+      <c r="C480" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D480" s="5" t="inlineStr">
         <is>
           <t>B.220 PLANT ROOM 04</t>
@@ -41572,7 +41684,11 @@
           <t>HEX</t>
         </is>
       </c>
-      <c r="C481" s="5" t="n"/>
+      <c r="C481" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D481" s="5" t="inlineStr">
         <is>
           <t>B.220 PLANT ROOM 04</t>
@@ -41598,7 +41714,11 @@
           <t>HEX</t>
         </is>
       </c>
-      <c r="C482" s="5" t="n"/>
+      <c r="C482" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D482" s="5" t="inlineStr">
         <is>
           <t>B.211 PH PLANT ROOM</t>
@@ -41624,7 +41744,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C483" s="5" t="n"/>
+      <c r="C483" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D483" s="5" t="inlineStr">
         <is>
           <t>L-3 L 3</t>
@@ -41650,7 +41774,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C484" s="5" t="n"/>
+      <c r="C484" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D484" s="5" t="inlineStr">
         <is>
           <t>B.085 FUMIGATION ROOM</t>
@@ -41676,7 +41804,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C485" s="5" t="n"/>
+      <c r="C485" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D485" s="5" t="inlineStr">
         <is>
           <t>B.055 DIGITIZATION CENTER</t>
@@ -41702,7 +41834,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C486" s="5" t="n"/>
+      <c r="C486" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D486" s="5" t="inlineStr">
         <is>
           <t>B.109 LOADING AREA</t>
@@ -41728,7 +41864,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C487" s="5" t="n"/>
+      <c r="C487" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D487" s="5" t="inlineStr">
         <is>
           <t>B.109 LOADING AREA</t>
@@ -41754,7 +41894,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C488" s="5" t="n"/>
+      <c r="C488" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D488" s="5" t="inlineStr">
         <is>
           <t>B.080 GENERATOR</t>
@@ -41780,7 +41924,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C489" s="5" t="n"/>
+      <c r="C489" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D489" s="5" t="inlineStr">
         <is>
           <t>B.093 TRANSH CHAMBER</t>
@@ -41806,7 +41954,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C490" s="5" t="n"/>
+      <c r="C490" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D490" s="5" t="inlineStr">
         <is>
           <t>B.091 FUEL ROOM</t>
@@ -41832,7 +41984,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C491" s="5" t="n"/>
+      <c r="C491" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D491" s="5" t="inlineStr">
         <is>
           <t>B.214 IDF ROOM</t>
@@ -41858,7 +42014,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C492" s="5" t="n"/>
+      <c r="C492" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D492" s="5" t="inlineStr">
         <is>
           <t>B.072 SPRIMKLERS PUMPS AND ZONES VALVES</t>
@@ -41884,7 +42044,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C493" s="5" t="n"/>
+      <c r="C493" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D493" s="5" t="inlineStr">
         <is>
           <t>B.064 CORRIDOR 2</t>
@@ -41910,7 +42074,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C494" s="5" t="n"/>
+      <c r="C494" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D494" s="5" t="inlineStr">
         <is>
           <t>B.109 LOADING AREA</t>
@@ -41936,7 +42104,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C495" s="5" t="n"/>
+      <c r="C495" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D495" s="5" t="inlineStr">
         <is>
           <t>B.109 LOADING AREA</t>
@@ -41962,7 +42134,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C496" s="5" t="n"/>
+      <c r="C496" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D496" s="5" t="inlineStr">
         <is>
           <t>B.070 PLANT ROOM 02</t>
@@ -41988,7 +42164,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C497" s="5" t="n"/>
+      <c r="C497" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D497" s="5" t="inlineStr">
         <is>
           <t>B.070 PLANT ROOM 02</t>
@@ -42014,7 +42194,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C498" s="5" t="n"/>
+      <c r="C498" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D498" s="5" t="inlineStr">
         <is>
           <t>P.002 PLANT ZONE</t>
@@ -42040,7 +42224,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C499" s="5" t="n"/>
+      <c r="C499" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D499" s="5" t="inlineStr">
         <is>
           <t>P.004 PLANT ZONE</t>
@@ -42066,7 +42254,11 @@
           <t>EF</t>
         </is>
       </c>
-      <c r="C500" s="5" t="n"/>
+      <c r="C500" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D500" s="5" t="inlineStr">
         <is>
           <t>P.007 PLANT ZONE</t>
@@ -42092,7 +42284,11 @@
           <t>KEF</t>
         </is>
       </c>
-      <c r="C501" s="5" t="n"/>
+      <c r="C501" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
           <t>L1.067 RESTAURANT</t>
@@ -42118,7 +42314,11 @@
           <t>KEF</t>
         </is>
       </c>
-      <c r="C502" s="5" t="n"/>
+      <c r="C502" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D502" s="5" t="inlineStr">
         <is>
           <t>B.049 MEP KITCHEN</t>
@@ -42144,7 +42344,11 @@
           <t>KEF</t>
         </is>
       </c>
-      <c r="C503" s="5" t="n"/>
+      <c r="C503" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D503" s="5" t="inlineStr">
         <is>
           <t>B.052 CORRIDOR 3</t>
@@ -42170,7 +42374,11 @@
           <t>KEF</t>
         </is>
       </c>
-      <c r="C504" s="5" t="n"/>
+      <c r="C504" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D504" s="5" t="inlineStr">
         <is>
           <t>B.001A BREAK OUT AREA</t>
@@ -42196,7 +42404,11 @@
           <t>SEF</t>
         </is>
       </c>
-      <c r="C505" s="5" t="n"/>
+      <c r="C505" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D505" s="5" t="inlineStr">
         <is>
           <t>P.002 PLANT ZONE</t>
@@ -42222,7 +42434,11 @@
           <t>SEF</t>
         </is>
       </c>
-      <c r="C506" s="5" t="n"/>
+      <c r="C506" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D506" s="5" t="inlineStr">
         <is>
           <t>P.002 PLANT ZONE</t>
@@ -42248,7 +42464,11 @@
           <t>SEF</t>
         </is>
       </c>
-      <c r="C507" s="5" t="n"/>
+      <c r="C507" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D507" s="5" t="inlineStr">
         <is>
           <t>P.002 PLANT ZONE</t>
@@ -42274,7 +42494,11 @@
           <t>SEF</t>
         </is>
       </c>
-      <c r="C508" s="5" t="n"/>
+      <c r="C508" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D508" s="5" t="inlineStr">
         <is>
           <t>P.004 PLANT ZONE</t>
@@ -42300,7 +42524,11 @@
           <t>SEF</t>
         </is>
       </c>
-      <c r="C509" s="5" t="n"/>
+      <c r="C509" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D509" s="5" t="inlineStr">
         <is>
           <t>P.004 PLANT ZONE</t>
@@ -42326,7 +42554,11 @@
           <t>SEF</t>
         </is>
       </c>
-      <c r="C510" s="5" t="n"/>
+      <c r="C510" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D510" s="5" t="inlineStr">
         <is>
           <t>P.004 PLANT ZONE</t>
@@ -42352,7 +42584,11 @@
           <t>SEF</t>
         </is>
       </c>
-      <c r="C511" s="5" t="n"/>
+      <c r="C511" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D511" s="5" t="inlineStr">
         <is>
           <t>P.007 PLANT ZONE</t>
@@ -42378,7 +42614,11 @@
           <t>SEF</t>
         </is>
       </c>
-      <c r="C512" s="5" t="n"/>
+      <c r="C512" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D512" s="5" t="inlineStr">
         <is>
           <t>P.006 PLANT ZONE</t>
@@ -42404,7 +42644,11 @@
           <t>SEF</t>
         </is>
       </c>
-      <c r="C513" s="5" t="n"/>
+      <c r="C513" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D513" s="5" t="inlineStr">
         <is>
           <t>P.006 PLANT ZONE</t>
@@ -42430,7 +42674,11 @@
           <t>SEF</t>
         </is>
       </c>
-      <c r="C514" s="5" t="n"/>
+      <c r="C514" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D514" s="5" t="inlineStr">
         <is>
           <t>P.002 PLANT ZONE</t>
@@ -42456,7 +42704,11 @@
           <t>SEF</t>
         </is>
       </c>
-      <c r="C515" s="5" t="n"/>
+      <c r="C515" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D515" s="5" t="inlineStr">
         <is>
           <t>P.004 PLANT ZONE</t>
@@ -42482,7 +42734,11 @@
           <t>SEF</t>
         </is>
       </c>
-      <c r="C516" s="5" t="n"/>
+      <c r="C516" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D516" s="5" t="inlineStr">
         <is>
           <t>P.007 PLANT ZONE</t>
@@ -42508,7 +42764,11 @@
           <t>TEF</t>
         </is>
       </c>
-      <c r="C517" s="5" t="n"/>
+      <c r="C517" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D517" s="5" t="inlineStr">
         <is>
           <t>E2 SHAFT</t>
@@ -42534,7 +42794,11 @@
           <t>TEF</t>
         </is>
       </c>
-      <c r="C518" s="5" t="n"/>
+      <c r="C518" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D518" s="5" t="inlineStr">
         <is>
           <t>E1 SHAFT</t>
@@ -42560,7 +42824,11 @@
           <t>TEF</t>
         </is>
       </c>
-      <c r="C519" s="5" t="n"/>
+      <c r="C519" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D519" s="5" t="inlineStr">
         <is>
           <t>B.110 PLANT ROOM 03</t>
@@ -42586,7 +42854,11 @@
           <t>TEF</t>
         </is>
       </c>
-      <c r="C520" s="5" t="n"/>
+      <c r="C520" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D520" s="5" t="inlineStr">
         <is>
           <t>B.110 PLANT ROOM 03</t>
@@ -42612,7 +42884,11 @@
           <t>TEF</t>
         </is>
       </c>
-      <c r="C521" s="5" t="n"/>
+      <c r="C521" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D521" s="5" t="inlineStr">
         <is>
           <t>B.070 PLANT ROOM 02</t>
@@ -42638,7 +42914,11 @@
           <t>TEF</t>
         </is>
       </c>
-      <c r="C522" s="5" t="n"/>
+      <c r="C522" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D522" s="5" t="inlineStr">
         <is>
           <t>B.070 PLANT ROOM 02</t>
@@ -42664,7 +42944,11 @@
           <t>TEF</t>
         </is>
       </c>
-      <c r="C523" s="5" t="n"/>
+      <c r="C523" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D523" s="5" t="inlineStr">
         <is>
           <t>B.120 COMPACT SHELVING MAIN COLLECTION</t>
@@ -42690,7 +42974,11 @@
           <t>TEF</t>
         </is>
       </c>
-      <c r="C524" s="5" t="n"/>
+      <c r="C524" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D524" s="5" t="inlineStr">
         <is>
           <t>B.120 COMPACT SHELVING MAIN COLLECTION</t>
@@ -42716,7 +43004,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C525" s="5" t="n"/>
+      <c r="C525" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D525" s="5" t="inlineStr">
         <is>
           <t>B.048 QTEL ROOM</t>
@@ -42742,7 +43034,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C526" s="5" t="n"/>
+      <c r="C526" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D526" s="5" t="inlineStr">
         <is>
           <t>B.048 QTEL ROOM</t>
@@ -42768,7 +43064,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C527" s="5" t="n"/>
+      <c r="C527" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
           <t>B.050 TELECOM ROOM</t>
@@ -42794,7 +43094,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C528" s="5" t="n"/>
+      <c r="C528" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D528" s="5" t="inlineStr">
         <is>
           <t>B.050 TELECOM ROOM</t>
@@ -42820,7 +43124,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C529" s="5" t="n"/>
+      <c r="C529" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
           <t>B.089 SERVER ROOM</t>
@@ -42846,7 +43154,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C530" s="5" t="n"/>
+      <c r="C530" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D530" s="5" t="inlineStr">
         <is>
           <t>B.089 SERVER ROOM</t>
@@ -42872,7 +43184,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C531" s="5" t="n"/>
+      <c r="C531" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
           <t>B.089 SERVER ROOM</t>
@@ -42898,7 +43214,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C532" s="5" t="n"/>
+      <c r="C532" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D532" s="5" t="inlineStr">
         <is>
           <t>B.141 VAULT</t>
@@ -42924,7 +43244,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C533" s="5" t="n"/>
+      <c r="C533" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D533" s="5" t="inlineStr">
         <is>
           <t>B.141 VAULT</t>
@@ -42950,7 +43274,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C534" s="5" t="n"/>
+      <c r="C534" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D534" s="5" t="inlineStr">
         <is>
           <t>B.222 IDF</t>
@@ -42976,7 +43304,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C535" s="5" t="n"/>
+      <c r="C535" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D535" s="5" t="inlineStr">
         <is>
           <t>B.222 IDF</t>
@@ -43002,7 +43334,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C536" s="5" t="n"/>
+      <c r="C536" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D536" s="6" t="n"/>
       <c r="E536" s="6" t="n"/>
       <c r="F536" s="6" t="n"/>
@@ -43024,7 +43360,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C537" s="5" t="n"/>
+      <c r="C537" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D537" s="6" t="n"/>
       <c r="E537" s="6" t="n"/>
       <c r="F537" s="6" t="n"/>
@@ -43046,7 +43386,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C538" s="5" t="n"/>
+      <c r="C538" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D538" s="6" t="n"/>
       <c r="E538" s="6" t="n"/>
       <c r="F538" s="6" t="n"/>
@@ -43068,7 +43412,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C539" s="5" t="n"/>
+      <c r="C539" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D539" s="6" t="n"/>
       <c r="E539" s="6" t="n"/>
       <c r="F539" s="6" t="n"/>
@@ -43090,7 +43438,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C540" s="5" t="n"/>
+      <c r="C540" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D540" s="6" t="n"/>
       <c r="E540" s="6" t="n"/>
       <c r="F540" s="6" t="n"/>
@@ -43112,7 +43464,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C541" s="5" t="n"/>
+      <c r="C541" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D541" s="6" t="n"/>
       <c r="E541" s="6" t="n"/>
       <c r="F541" s="6" t="n"/>
@@ -43134,7 +43490,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C542" s="5" t="n"/>
+      <c r="C542" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D542" s="6" t="n"/>
       <c r="E542" s="6" t="n"/>
       <c r="F542" s="6" t="n"/>
@@ -43156,7 +43516,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C543" s="5" t="n"/>
+      <c r="C543" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D543" s="6" t="n"/>
       <c r="E543" s="6" t="n"/>
       <c r="F543" s="6" t="n"/>
@@ -43178,7 +43542,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C544" s="5" t="n"/>
+      <c r="C544" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D544" s="6" t="n"/>
       <c r="E544" s="6" t="n"/>
       <c r="F544" s="6" t="n"/>
@@ -43200,7 +43568,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C545" s="5" t="n"/>
+      <c r="C545" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D545" s="6" t="n"/>
       <c r="E545" s="6" t="n"/>
       <c r="F545" s="6" t="n"/>
@@ -43222,7 +43594,11 @@
           <t>CCU</t>
         </is>
       </c>
-      <c r="C546" s="5" t="n"/>
+      <c r="C546" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D546" s="6" t="n"/>
       <c r="E546" s="6" t="n"/>
       <c r="F546" s="6" t="n"/>
@@ -43244,7 +43620,11 @@
           <t>CHW Pump</t>
         </is>
       </c>
-      <c r="C547" s="5" t="n"/>
+      <c r="C547" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D547" s="5" t="inlineStr">
         <is>
           <t>B.220 PLANT ROOM 04</t>
@@ -43270,7 +43650,11 @@
           <t>CHW Pump</t>
         </is>
       </c>
-      <c r="C548" s="5" t="n"/>
+      <c r="C548" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D548" s="5" t="inlineStr">
         <is>
           <t>B.220 PLANT ROOM 04</t>
@@ -43296,7 +43680,11 @@
           <t>CHW Pump</t>
         </is>
       </c>
-      <c r="C549" s="5" t="n"/>
+      <c r="C549" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
           <t>B.220 PLANT ROOM 04</t>
@@ -43322,7 +43710,11 @@
           <t>CHW Pump</t>
         </is>
       </c>
-      <c r="C550" s="5" t="n"/>
+      <c r="C550" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D550" s="5" t="inlineStr">
         <is>
           <t>B.220 PLANT ROOM 04</t>
@@ -43348,7 +43740,11 @@
           <t>CHW Pump</t>
         </is>
       </c>
-      <c r="C551" s="5" t="n"/>
+      <c r="C551" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D551" s="5" t="inlineStr">
         <is>
           <t>B.220 PLANT ROOM 04</t>
@@ -43374,7 +43770,11 @@
           <t>CHW Pump</t>
         </is>
       </c>
-      <c r="C552" s="5" t="n"/>
+      <c r="C552" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D552" s="6" t="n"/>
       <c r="E552" s="6" t="n"/>
       <c r="F552" s="6" t="n"/>
@@ -43396,7 +43796,11 @@
           <t>Generator</t>
         </is>
       </c>
-      <c r="C553" s="5" t="n"/>
+      <c r="C553" s="6" t="inlineStr">
+        <is>
+          <t>Not Included</t>
+        </is>
+      </c>
       <c r="D553" s="5" t="inlineStr">
         <is>
           <t>B.080 GENERATOR</t>

--- a/projects/register-room-update/All_Buildings_Rooms_Inclusion_Status_V1.3.xlsx
+++ b/projects/register-room-update/All_Buildings_Rooms_Inclusion_Status_V1.3.xlsx
@@ -49457,7 +49457,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -49502,7 +49502,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -49547,7 +49547,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -49592,7 +49592,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -49637,7 +49637,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -49682,7 +49682,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -49729,7 +49729,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -50340,7 +50340,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -50369,7 +50369,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -50398,7 +50398,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -50427,7 +50427,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -50456,7 +50456,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -50485,7 +50485,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -50514,7 +50514,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -50543,7 +50543,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -50572,7 +50572,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -50601,7 +50601,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -50630,7 +50630,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -50978,7 +50978,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -51007,7 +51007,7 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -51036,7 +51036,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -51065,7 +51065,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -51094,7 +51094,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -51123,7 +51123,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -51152,7 +51152,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -51964,7 +51964,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -51993,7 +51993,7 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -52022,7 +52022,7 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -52051,7 +52051,7 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -52080,7 +52080,7 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -52109,7 +52109,7 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -52138,7 +52138,7 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -52167,7 +52167,7 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -52631,7 +52631,7 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -52660,7 +52660,7 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -52718,7 +52718,7 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -52747,7 +52747,7 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -52776,7 +52776,7 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -52805,7 +52805,7 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
@@ -52863,7 +52863,7 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -52892,7 +52892,7 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -52921,7 +52921,7 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
@@ -54922,7 +54922,7 @@
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
@@ -54951,7 +54951,7 @@
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
@@ -54980,7 +54980,7 @@
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
@@ -55009,7 +55009,7 @@
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
@@ -55067,7 +55067,7 @@
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
@@ -55096,7 +55096,7 @@
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
@@ -55125,7 +55125,7 @@
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
@@ -55154,7 +55154,7 @@
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
@@ -55183,7 +55183,7 @@
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
@@ -55212,7 +55212,7 @@
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
@@ -55241,7 +55241,7 @@
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
@@ -55966,7 +55966,7 @@
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
@@ -55995,7 +55995,7 @@
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
@@ -56053,7 +56053,7 @@
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
@@ -56082,7 +56082,7 @@
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
@@ -56111,7 +56111,7 @@
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
@@ -56140,7 +56140,7 @@
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
@@ -56169,7 +56169,7 @@
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
@@ -56198,7 +56198,7 @@
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
@@ -56227,7 +56227,7 @@
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
@@ -56256,7 +56256,7 @@
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
@@ -56285,7 +56285,7 @@
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
@@ -56314,7 +56314,7 @@
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
@@ -56343,7 +56343,7 @@
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
@@ -56372,7 +56372,7 @@
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
@@ -57068,7 +57068,7 @@
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
@@ -57619,7 +57619,7 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
@@ -58257,7 +58257,7 @@
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
@@ -58286,7 +58286,7 @@
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D319" s="5" t="inlineStr">
@@ -58344,7 +58344,7 @@
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
@@ -58373,7 +58373,7 @@
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
@@ -61563,7 +61563,7 @@
       </c>
       <c r="C432" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D432" s="5" t="inlineStr">
@@ -61679,7 +61679,7 @@
       </c>
       <c r="C436" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D436" s="5" t="inlineStr">
@@ -61795,7 +61795,7 @@
       </c>
       <c r="C440" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D440" s="5" t="inlineStr">
@@ -61911,7 +61911,7 @@
       </c>
       <c r="C444" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D444" s="5" t="inlineStr">
@@ -64869,7 +64869,7 @@
       </c>
       <c r="C546" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D546" s="5" t="inlineStr">
@@ -64898,7 +64898,7 @@
       </c>
       <c r="C547" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D547" s="5" t="inlineStr">
@@ -64927,7 +64927,7 @@
       </c>
       <c r="C548" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D548" s="5" t="inlineStr">
@@ -64956,7 +64956,7 @@
       </c>
       <c r="C549" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D549" s="5" t="inlineStr">
@@ -64985,7 +64985,7 @@
       </c>
       <c r="C550" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D550" s="5" t="inlineStr">
@@ -65855,7 +65855,7 @@
       </c>
       <c r="C580" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D580" s="5" t="inlineStr">
@@ -65884,7 +65884,7 @@
       </c>
       <c r="C581" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D581" s="5" t="inlineStr">
@@ -65913,7 +65913,7 @@
       </c>
       <c r="C582" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D582" s="5" t="inlineStr">
@@ -65942,7 +65942,7 @@
       </c>
       <c r="C583" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D583" s="5" t="inlineStr">
@@ -65971,7 +65971,7 @@
       </c>
       <c r="C584" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D584" s="5" t="inlineStr">
@@ -66000,7 +66000,7 @@
       </c>
       <c r="C585" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D585" s="5" t="inlineStr">
@@ -66058,7 +66058,7 @@
       </c>
       <c r="C587" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D587" s="5" t="inlineStr">
@@ -66087,7 +66087,7 @@
       </c>
       <c r="C588" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D588" s="5" t="inlineStr">
@@ -66116,7 +66116,7 @@
       </c>
       <c r="C589" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D589" s="5" t="inlineStr">
@@ -66145,7 +66145,7 @@
       </c>
       <c r="C590" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D590" s="5" t="inlineStr">
@@ -66725,7 +66725,7 @@
       </c>
       <c r="C610" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D610" s="5" t="inlineStr">
@@ -66754,7 +66754,7 @@
       </c>
       <c r="C611" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D611" s="5" t="inlineStr">
@@ -66783,7 +66783,7 @@
       </c>
       <c r="C612" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D612" s="5" t="inlineStr">
@@ -66812,7 +66812,7 @@
       </c>
       <c r="C613" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D613" s="5" t="inlineStr">
@@ -66870,7 +66870,7 @@
       </c>
       <c r="C615" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D615" s="5" t="inlineStr">
@@ -66899,7 +66899,7 @@
       </c>
       <c r="C616" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D616" s="5" t="inlineStr">
@@ -66928,7 +66928,7 @@
       </c>
       <c r="C617" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D617" s="5" t="inlineStr">
@@ -67740,7 +67740,7 @@
       </c>
       <c r="C645" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D645" s="5" t="inlineStr">
@@ -67769,7 +67769,7 @@
       </c>
       <c r="C646" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D646" s="5" t="inlineStr">
@@ -67798,7 +67798,7 @@
       </c>
       <c r="C647" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D647" s="5" t="inlineStr">
@@ -67827,7 +67827,7 @@
       </c>
       <c r="C648" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D648" s="5" t="inlineStr">
@@ -67856,7 +67856,7 @@
       </c>
       <c r="C649" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D649" s="5" t="inlineStr">
@@ -67914,7 +67914,7 @@
       </c>
       <c r="C651" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D651" s="5" t="inlineStr">
@@ -67943,7 +67943,7 @@
       </c>
       <c r="C652" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D652" s="5" t="inlineStr">
@@ -67972,7 +67972,7 @@
       </c>
       <c r="C653" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D653" s="5" t="inlineStr">
@@ -68001,7 +68001,7 @@
       </c>
       <c r="C654" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D654" s="5" t="inlineStr">
@@ -68030,7 +68030,7 @@
       </c>
       <c r="C655" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D655" s="5" t="inlineStr">
@@ -68059,7 +68059,7 @@
       </c>
       <c r="C656" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D656" s="5" t="inlineStr">
@@ -68088,7 +68088,7 @@
       </c>
       <c r="C657" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D657" s="5" t="inlineStr">
@@ -68117,7 +68117,7 @@
       </c>
       <c r="C658" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D658" s="5" t="inlineStr">
@@ -68610,7 +68610,7 @@
       </c>
       <c r="C675" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D675" s="5" t="inlineStr">
@@ -68639,7 +68639,7 @@
       </c>
       <c r="C676" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D676" s="5" t="inlineStr">
@@ -68668,7 +68668,7 @@
       </c>
       <c r="C677" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D677" s="5" t="inlineStr">
@@ -68697,7 +68697,7 @@
       </c>
       <c r="C678" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D678" s="5" t="inlineStr">
@@ -68726,7 +68726,7 @@
       </c>
       <c r="C679" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D679" s="5" t="inlineStr">
@@ -68755,7 +68755,7 @@
       </c>
       <c r="C680" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D680" s="5" t="inlineStr">
@@ -68784,7 +68784,7 @@
       </c>
       <c r="C681" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D681" s="5" t="inlineStr">
@@ -68813,7 +68813,7 @@
       </c>
       <c r="C682" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D682" s="5" t="inlineStr">
@@ -68842,7 +68842,7 @@
       </c>
       <c r="C683" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D683" s="5" t="inlineStr">
@@ -68871,7 +68871,7 @@
       </c>
       <c r="C684" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D684" s="5" t="inlineStr">
@@ -69712,7 +69712,7 @@
       </c>
       <c r="C713" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D713" s="5" t="inlineStr">
@@ -69741,7 +69741,7 @@
       </c>
       <c r="C714" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D714" s="5" t="inlineStr">
@@ -69770,7 +69770,7 @@
       </c>
       <c r="C715" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D715" s="5" t="inlineStr">
@@ -69799,7 +69799,7 @@
       </c>
       <c r="C716" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D716" s="5" t="inlineStr">
@@ -69828,7 +69828,7 @@
       </c>
       <c r="C717" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D717" s="5" t="inlineStr">
@@ -69857,7 +69857,7 @@
       </c>
       <c r="C718" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D718" s="5" t="inlineStr">
@@ -69886,7 +69886,7 @@
       </c>
       <c r="C719" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D719" s="5" t="inlineStr">
@@ -69915,7 +69915,7 @@
       </c>
       <c r="C720" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D720" s="5" t="inlineStr">
@@ -69944,7 +69944,7 @@
       </c>
       <c r="C721" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D721" s="5" t="inlineStr">
@@ -70524,7 +70524,7 @@
       </c>
       <c r="C741" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D741" s="5" t="inlineStr">
@@ -70553,7 +70553,7 @@
       </c>
       <c r="C742" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D742" s="5" t="inlineStr">
@@ -70582,7 +70582,7 @@
       </c>
       <c r="C743" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D743" s="5" t="inlineStr">
@@ -70611,7 +70611,7 @@
       </c>
       <c r="C744" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D744" s="5" t="inlineStr">
@@ -70640,7 +70640,7 @@
       </c>
       <c r="C745" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D745" s="5" t="inlineStr">
@@ -70669,7 +70669,7 @@
       </c>
       <c r="C746" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D746" s="5" t="inlineStr">
@@ -70698,7 +70698,7 @@
       </c>
       <c r="C747" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D747" s="5" t="inlineStr">
@@ -70727,7 +70727,7 @@
       </c>
       <c r="C748" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D748" s="5" t="inlineStr">
@@ -70756,7 +70756,7 @@
       </c>
       <c r="C749" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D749" s="5" t="inlineStr">
@@ -70785,7 +70785,7 @@
       </c>
       <c r="C750" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D750" s="5" t="inlineStr">
@@ -71742,7 +71742,7 @@
       </c>
       <c r="C783" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D783" s="5" t="inlineStr">
@@ -72699,7 +72699,7 @@
       </c>
       <c r="C816" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D816" s="5" t="inlineStr">
@@ -72728,7 +72728,7 @@
       </c>
       <c r="C817" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D817" s="5" t="inlineStr">
@@ -73047,7 +73047,7 @@
       </c>
       <c r="C828" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D828" s="5" t="inlineStr">
@@ -73076,7 +73076,7 @@
       </c>
       <c r="C829" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D829" s="5" t="inlineStr">
@@ -74786,7 +74786,7 @@
       </c>
       <c r="C883" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D883" s="5" t="inlineStr">
@@ -74885,7 +74885,7 @@
       </c>
       <c r="C886" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D886" s="5" t="inlineStr">
@@ -74918,7 +74918,7 @@
       </c>
       <c r="C887" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D887" s="5" t="inlineStr">
@@ -74951,7 +74951,7 @@
       </c>
       <c r="C888" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D888" s="5" t="inlineStr">
@@ -75021,7 +75021,7 @@
       </c>
       <c r="C890" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D890" s="5" t="inlineStr">
@@ -75056,7 +75056,7 @@
       </c>
       <c r="C891" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D891" s="5" t="inlineStr">
@@ -76154,7 +76154,7 @@
       </c>
       <c r="C925" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D925" s="5" t="inlineStr">
@@ -76183,7 +76183,7 @@
       </c>
       <c r="C926" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D926" s="5" t="inlineStr">
@@ -76212,7 +76212,7 @@
       </c>
       <c r="C927" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D927" s="5" t="inlineStr">
@@ -76241,7 +76241,7 @@
       </c>
       <c r="C928" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D928" s="5" t="inlineStr">
@@ -76270,7 +76270,7 @@
       </c>
       <c r="C929" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D929" s="5" t="inlineStr">
@@ -76299,7 +76299,7 @@
       </c>
       <c r="C930" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D930" s="5" t="inlineStr">
@@ -76328,7 +76328,7 @@
       </c>
       <c r="C931" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D931" s="5" t="inlineStr">
@@ -76357,7 +76357,7 @@
       </c>
       <c r="C932" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D932" s="5" t="inlineStr">
@@ -76846,7 +76846,7 @@
       </c>
       <c r="C949" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D949" s="5" t="inlineStr">
@@ -76875,7 +76875,7 @@
       </c>
       <c r="C950" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D950" s="5" t="inlineStr">
@@ -76904,7 +76904,7 @@
       </c>
       <c r="C951" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D951" s="5" t="inlineStr">
@@ -76933,7 +76933,7 @@
       </c>
       <c r="C952" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D952" s="5" t="inlineStr">
@@ -76962,7 +76962,7 @@
       </c>
       <c r="C953" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D953" s="5" t="inlineStr">
@@ -76991,7 +76991,7 @@
       </c>
       <c r="C954" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D954" s="5" t="inlineStr">
@@ -77020,7 +77020,7 @@
       </c>
       <c r="C955" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D955" s="5" t="inlineStr">
@@ -77049,7 +77049,7 @@
       </c>
       <c r="C956" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D956" s="5" t="inlineStr">
@@ -77078,7 +77078,7 @@
       </c>
       <c r="C957" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D957" s="5" t="inlineStr">
@@ -77107,7 +77107,7 @@
       </c>
       <c r="C958" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D958" s="5" t="inlineStr">
@@ -77136,7 +77136,7 @@
       </c>
       <c r="C959" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D959" s="5" t="inlineStr">
@@ -77165,7 +77165,7 @@
       </c>
       <c r="C960" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D960" s="5" t="inlineStr">
@@ -77194,7 +77194,7 @@
       </c>
       <c r="C961" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D961" s="5" t="inlineStr">
@@ -77223,7 +77223,7 @@
       </c>
       <c r="C962" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D962" s="5" t="inlineStr">
@@ -77252,7 +77252,7 @@
       </c>
       <c r="C963" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D963" s="5" t="inlineStr">
@@ -77281,7 +77281,7 @@
       </c>
       <c r="C964" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D964" s="5" t="inlineStr">
@@ -77310,7 +77310,7 @@
       </c>
       <c r="C965" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D965" s="5" t="inlineStr">
@@ -77339,7 +77339,7 @@
       </c>
       <c r="C966" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D966" s="5" t="inlineStr">
@@ -77368,7 +77368,7 @@
       </c>
       <c r="C967" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D967" s="5" t="inlineStr">
@@ -77455,7 +77455,7 @@
       </c>
       <c r="C970" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D970" s="5" t="inlineStr">
@@ -77484,7 +77484,7 @@
       </c>
       <c r="C971" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D971" s="5" t="inlineStr">
@@ -77513,7 +77513,7 @@
       </c>
       <c r="C972" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D972" s="5" t="inlineStr">
@@ -77542,7 +77542,7 @@
       </c>
       <c r="C973" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D973" s="5" t="inlineStr">
@@ -77571,7 +77571,7 @@
       </c>
       <c r="C974" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D974" s="5" t="inlineStr">
@@ -77600,7 +77600,7 @@
       </c>
       <c r="C975" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D975" s="5" t="inlineStr">
@@ -77629,7 +77629,7 @@
       </c>
       <c r="C976" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D976" s="5" t="inlineStr">
@@ -77658,7 +77658,7 @@
       </c>
       <c r="C977" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D977" s="5" t="inlineStr">
@@ -77687,7 +77687,7 @@
       </c>
       <c r="C978" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D978" s="5" t="inlineStr">
@@ -77716,7 +77716,7 @@
       </c>
       <c r="C979" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D979" s="5" t="inlineStr">
@@ -77745,7 +77745,7 @@
       </c>
       <c r="C980" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D980" s="5" t="inlineStr">
@@ -77774,7 +77774,7 @@
       </c>
       <c r="C981" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D981" s="5" t="inlineStr">
@@ -77803,7 +77803,7 @@
       </c>
       <c r="C982" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D982" s="5" t="inlineStr">
@@ -77832,7 +77832,7 @@
       </c>
       <c r="C983" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D983" s="5" t="inlineStr">
@@ -78611,7 +78611,7 @@
       </c>
       <c r="C1010" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1010" s="5" t="inlineStr">
@@ -78640,7 +78640,7 @@
       </c>
       <c r="C1011" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1011" s="5" t="inlineStr">
@@ -78669,7 +78669,7 @@
       </c>
       <c r="C1012" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1012" s="5" t="inlineStr">
@@ -78698,7 +78698,7 @@
       </c>
       <c r="C1013" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1013" s="5" t="inlineStr">
@@ -78727,7 +78727,7 @@
       </c>
       <c r="C1014" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1014" s="5" t="inlineStr">
@@ -78756,7 +78756,7 @@
       </c>
       <c r="C1015" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1015" s="5" t="inlineStr">
@@ -78785,7 +78785,7 @@
       </c>
       <c r="C1016" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1016" s="5" t="inlineStr">
@@ -78814,7 +78814,7 @@
       </c>
       <c r="C1017" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1017" s="5" t="inlineStr">
@@ -78843,7 +78843,7 @@
       </c>
       <c r="C1018" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1018" s="5" t="inlineStr">
@@ -78872,7 +78872,7 @@
       </c>
       <c r="C1019" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1019" s="5" t="inlineStr">
@@ -78901,7 +78901,7 @@
       </c>
       <c r="C1020" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1020" s="5" t="inlineStr">
@@ -78930,7 +78930,7 @@
       </c>
       <c r="C1021" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1021" s="5" t="inlineStr">
@@ -78959,7 +78959,7 @@
       </c>
       <c r="C1022" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1022" s="5" t="inlineStr">
@@ -78988,7 +78988,7 @@
       </c>
       <c r="C1023" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1023" s="5" t="inlineStr">
@@ -79017,7 +79017,7 @@
       </c>
       <c r="C1024" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1024" s="5" t="inlineStr">
@@ -79046,7 +79046,7 @@
       </c>
       <c r="C1025" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1025" s="5" t="inlineStr">
@@ -79075,7 +79075,7 @@
       </c>
       <c r="C1026" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1026" s="5" t="inlineStr">
@@ -79365,7 +79365,7 @@
       </c>
       <c r="C1036" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1036" s="5" t="inlineStr">
@@ -79394,7 +79394,7 @@
       </c>
       <c r="C1037" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1037" s="5" t="inlineStr">
@@ -79423,7 +79423,7 @@
       </c>
       <c r="C1038" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1038" s="5" t="inlineStr">
@@ -79452,7 +79452,7 @@
       </c>
       <c r="C1039" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1039" s="5" t="inlineStr">
@@ -79481,7 +79481,7 @@
       </c>
       <c r="C1040" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1040" s="5" t="inlineStr">
@@ -79510,7 +79510,7 @@
       </c>
       <c r="C1041" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1041" s="5" t="inlineStr">
@@ -79539,7 +79539,7 @@
       </c>
       <c r="C1042" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1042" s="5" t="inlineStr">
@@ -79568,7 +79568,7 @@
       </c>
       <c r="C1043" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1043" s="5" t="inlineStr">
@@ -79597,7 +79597,7 @@
       </c>
       <c r="C1044" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1044" s="5" t="inlineStr">
@@ -79626,7 +79626,7 @@
       </c>
       <c r="C1045" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1045" s="5" t="inlineStr">
@@ -79655,7 +79655,7 @@
       </c>
       <c r="C1046" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1046" s="5" t="inlineStr">
@@ -79684,7 +79684,7 @@
       </c>
       <c r="C1047" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1047" s="5" t="inlineStr">
@@ -79713,7 +79713,7 @@
       </c>
       <c r="C1048" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1048" s="5" t="inlineStr">
@@ -80351,7 +80351,7 @@
       </c>
       <c r="C1070" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1070" s="5" t="inlineStr">
@@ -80380,7 +80380,7 @@
       </c>
       <c r="C1071" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1071" s="5" t="inlineStr">
@@ -80409,7 +80409,7 @@
       </c>
       <c r="C1072" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1072" s="5" t="inlineStr">
@@ -80438,7 +80438,7 @@
       </c>
       <c r="C1073" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1073" s="5" t="inlineStr">
@@ -80467,7 +80467,7 @@
       </c>
       <c r="C1074" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1074" s="5" t="inlineStr">
@@ -80496,7 +80496,7 @@
       </c>
       <c r="C1075" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1075" s="5" t="inlineStr">
@@ -80525,7 +80525,7 @@
       </c>
       <c r="C1076" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1076" s="5" t="inlineStr">
@@ -80554,7 +80554,7 @@
       </c>
       <c r="C1077" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1077" s="5" t="inlineStr">
@@ -80583,7 +80583,7 @@
       </c>
       <c r="C1078" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1078" s="5" t="inlineStr">
@@ -80641,7 +80641,7 @@
       </c>
       <c r="C1080" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1080" s="5" t="inlineStr">
@@ -80670,7 +80670,7 @@
       </c>
       <c r="C1081" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1081" s="5" t="inlineStr">
@@ -80699,7 +80699,7 @@
       </c>
       <c r="C1082" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1082" s="5" t="inlineStr">
@@ -80728,7 +80728,7 @@
       </c>
       <c r="C1083" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1083" s="5" t="inlineStr">
@@ -80757,7 +80757,7 @@
       </c>
       <c r="C1084" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1084" s="5" t="inlineStr">
@@ -80786,7 +80786,7 @@
       </c>
       <c r="C1085" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1085" s="5" t="inlineStr">
@@ -81076,7 +81076,7 @@
       </c>
       <c r="C1095" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1095" s="5" t="inlineStr">
@@ -81105,7 +81105,7 @@
       </c>
       <c r="C1096" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1096" s="5" t="inlineStr">
@@ -81134,7 +81134,7 @@
       </c>
       <c r="C1097" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1097" s="5" t="inlineStr">
@@ -81163,7 +81163,7 @@
       </c>
       <c r="C1098" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1098" s="5" t="inlineStr">
@@ -81192,7 +81192,7 @@
       </c>
       <c r="C1099" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1099" s="5" t="inlineStr">
@@ -81221,7 +81221,7 @@
       </c>
       <c r="C1100" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1100" s="5" t="inlineStr">
@@ -81250,7 +81250,7 @@
       </c>
       <c r="C1101" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1101" s="5" t="inlineStr">
@@ -81279,7 +81279,7 @@
       </c>
       <c r="C1102" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1102" s="5" t="inlineStr">
@@ -81308,7 +81308,7 @@
       </c>
       <c r="C1103" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1103" s="5" t="inlineStr">
@@ -81337,7 +81337,7 @@
       </c>
       <c r="C1104" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1104" s="5" t="inlineStr">
@@ -81366,7 +81366,7 @@
       </c>
       <c r="C1105" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1105" s="5" t="inlineStr">
@@ -81395,7 +81395,7 @@
       </c>
       <c r="C1106" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1106" s="5" t="inlineStr">
@@ -81424,7 +81424,7 @@
       </c>
       <c r="C1107" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1107" s="5" t="inlineStr">
@@ -81453,7 +81453,7 @@
       </c>
       <c r="C1108" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1108" s="5" t="inlineStr">
@@ -81482,7 +81482,7 @@
       </c>
       <c r="C1109" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1109" s="5" t="inlineStr">
@@ -81540,7 +81540,7 @@
       </c>
       <c r="C1111" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1111" s="5" t="inlineStr">
@@ -81569,7 +81569,7 @@
       </c>
       <c r="C1112" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1112" s="5" t="inlineStr">
@@ -81598,7 +81598,7 @@
       </c>
       <c r="C1113" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1113" s="5" t="inlineStr">
@@ -81627,7 +81627,7 @@
       </c>
       <c r="C1114" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1114" s="5" t="inlineStr">
@@ -81656,7 +81656,7 @@
       </c>
       <c r="C1115" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1115" s="5" t="inlineStr">
@@ -81685,7 +81685,7 @@
       </c>
       <c r="C1116" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1116" s="5" t="inlineStr">
@@ -81714,7 +81714,7 @@
       </c>
       <c r="C1117" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1117" s="5" t="inlineStr">
@@ -81743,7 +81743,7 @@
       </c>
       <c r="C1118" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1118" s="5" t="inlineStr">
@@ -81772,7 +81772,7 @@
       </c>
       <c r="C1119" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1119" s="5" t="inlineStr">
@@ -81801,7 +81801,7 @@
       </c>
       <c r="C1120" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1120" s="5" t="inlineStr">
@@ -81830,7 +81830,7 @@
       </c>
       <c r="C1121" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1121" s="5" t="inlineStr">
@@ -81859,7 +81859,7 @@
       </c>
       <c r="C1122" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1122" s="5" t="inlineStr">
@@ -81888,7 +81888,7 @@
       </c>
       <c r="C1123" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1123" s="5" t="inlineStr">
@@ -81917,7 +81917,7 @@
       </c>
       <c r="C1124" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1124" s="5" t="inlineStr">
@@ -81946,7 +81946,7 @@
       </c>
       <c r="C1125" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1125" s="5" t="inlineStr">
@@ -82207,7 +82207,7 @@
       </c>
       <c r="C1134" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1134" s="5" t="inlineStr">
@@ -82236,7 +82236,7 @@
       </c>
       <c r="C1135" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1135" s="5" t="inlineStr">
@@ -82265,7 +82265,7 @@
       </c>
       <c r="C1136" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1136" s="5" t="inlineStr">
@@ -82294,7 +82294,7 @@
       </c>
       <c r="C1137" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1137" s="5" t="inlineStr">
@@ -82323,7 +82323,7 @@
       </c>
       <c r="C1138" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1138" s="5" t="inlineStr">
@@ -82352,7 +82352,7 @@
       </c>
       <c r="C1139" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1139" s="5" t="inlineStr">
@@ -82381,7 +82381,7 @@
       </c>
       <c r="C1140" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1140" s="5" t="inlineStr">
@@ -82410,7 +82410,7 @@
       </c>
       <c r="C1141" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D1141" s="5" t="inlineStr">

--- a/projects/register-room-update/All_Buildings_Rooms_Inclusion_Status_V1.3.xlsx
+++ b/projects/register-room-update/All_Buildings_Rooms_Inclusion_Status_V1.3.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D337" s="5" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="C415" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D415" s="5" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="C416" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D416" s="5" t="inlineStr">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="C443" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D443" s="5" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C444" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D444" s="5" t="inlineStr">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="C445" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D445" s="5" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="C446" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D446" s="5" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="C453" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D453" s="5" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="C474" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D474" s="5" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="C497" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D497" s="5" t="inlineStr">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="C498" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D498" s="5" t="inlineStr">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="C535" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D535" s="5" t="inlineStr">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="C536" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D536" s="5" t="inlineStr">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="C537" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D537" s="5" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="C538" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D538" s="5" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="C539" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D539" s="5" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="C540" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D540" s="5" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="C541" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D541" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="C542" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D542" s="5" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="C543" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D543" s="5" t="inlineStr">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="C580" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D580" s="5" t="inlineStr">
@@ -17968,7 +17968,7 @@
       </c>
       <c r="C582" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D582" s="5" t="inlineStr">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C583" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D583" s="5" t="inlineStr">
@@ -18084,7 +18084,7 @@
       </c>
       <c r="C586" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D586" s="5" t="inlineStr">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="C587" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D587" s="5" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="C588" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D588" s="5" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="C610" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D610" s="5" t="inlineStr">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C611" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D611" s="5" t="inlineStr">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="C612" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D612" s="5" t="inlineStr">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="C615" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D615" s="5" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="C616" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D616" s="5" t="inlineStr">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C617" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D617" s="5" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C618" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D618" s="5" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="C619" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D619" s="5" t="inlineStr">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="C620" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D620" s="5" t="inlineStr">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="C621" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D621" s="5" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="C622" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D622" s="5" t="inlineStr">
@@ -19157,7 +19157,7 @@
       </c>
       <c r="C623" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D623" s="5" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="C630" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D630" s="5" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="C645" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D645" s="5" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C646" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D646" s="5" t="inlineStr">
@@ -19853,7 +19853,7 @@
       </c>
       <c r="C647" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D647" s="5" t="inlineStr">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="C655" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D655" s="5" t="inlineStr">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C731" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D731" s="5" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="C732" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D732" s="5" t="inlineStr">
@@ -22368,7 +22368,7 @@
       </c>
       <c r="C734" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D734" s="5" t="inlineStr">
@@ -23384,7 +23384,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -23418,7 +23418,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -23554,7 +23554,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -23896,7 +23896,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -26088,7 +26088,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -27776,7 +27776,7 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -28796,7 +28796,7 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="C331" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D331" s="5" t="inlineStr">
@@ -37188,7 +37188,7 @@
       </c>
       <c r="C359" s="5" t="inlineStr">
         <is>
-          <t>Included</t>
+          <t>Not Included</t>
         </is>
       </c>
       <c r="D359" s="5" t="inlineStr">
@@ -38452,7 +38452,7 @@
       </c>
       <c r="C391" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D391" s="5" t="inlineStr">
@@ -38492,7 +38492,7 @@
       </c>
       <c r="C392" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D392" s="5" t="inlineStr">
@@ -38532,7 +38532,7 @@
       </c>
       <c r="C393" s="5" t="inlineStr">
         <is>
-          <t>Not Included</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="D393" s="5" t="inlineStr">
